--- a/dados_tracker/tracker_dados.xlsx
+++ b/dados_tracker/tracker_dados.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Agentes'!$A$1:$U$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapas'!$A$1:$Q$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapas'!$A$1:$A$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1873,602 +1873,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Map Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Top Agents</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Win %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Wins</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Losses</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>K/D</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ADR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>ACS</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>DDΔ</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>HS%</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Aces</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Clutches</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Thrifty</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Flawless</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Plants</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Defuses</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Haven</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Jett (67%); Clove (50%); Phoenix (40%)</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="E2" t="n">
-        <v>15</v>
-      </c>
-      <c r="F2" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H2" t="n">
-        <v>139.1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>204</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>15</v>
-      </c>
-      <c r="N2" t="n">
-        <v>14</v>
-      </c>
-      <c r="O2" t="n">
-        <v>16</v>
-      </c>
-      <c r="P2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Summit</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Jett (83%); Clove (43%)</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>145.3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>218.8</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3</v>
-      </c>
-      <c r="N3" t="n">
-        <v>10</v>
-      </c>
-      <c r="O3" t="n">
-        <v>13</v>
-      </c>
-      <c r="P3" t="n">
-        <v>25</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ascent</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Sova (60%); Clove (46%)</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="E4" t="n">
-        <v>13</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>150.6</v>
-      </c>
-      <c r="I4" t="n">
-        <v>222.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>9</v>
-      </c>
-      <c r="N4" t="n">
-        <v>9</v>
-      </c>
-      <c r="O4" t="n">
-        <v>14</v>
-      </c>
-      <c r="P4" t="n">
-        <v>45</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sunset</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Clove (67%)</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="E5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F5" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="H5" t="n">
-        <v>147.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>215.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6</v>
-      </c>
-      <c r="N5" t="n">
-        <v>7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>18</v>
-      </c>
-      <c r="P5" t="n">
-        <v>34</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Lotus</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Jett (50%); Clove (30%)</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>8</v>
-      </c>
-      <c r="F6" t="n">
-        <v>13</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="H6" t="n">
-        <v>140</v>
-      </c>
-      <c r="I6" t="n">
-        <v>213.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K6" t="n">
-        <v>29.8</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>6</v>
-      </c>
-      <c r="N6" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" t="n">
-        <v>11</v>
-      </c>
-      <c r="P6" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Breeze</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Sova (40%); Clove (33%); Jett (20%)</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>8</v>
-      </c>
-      <c r="F7" t="n">
-        <v>15</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H7" t="n">
-        <v>143.8</v>
-      </c>
-      <c r="I7" t="n">
-        <v>213.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>-8</v>
-      </c>
-      <c r="K7" t="n">
-        <v>33.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N7" t="n">
-        <v>9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>12</v>
-      </c>
-      <c r="P7" t="n">
-        <v>44</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mapa</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Split</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Clove (22%); Jett (0%)</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>20</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>15</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="H8" t="n">
-        <v>139.4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>210.6</v>
-      </c>
-      <c r="J8" t="n">
-        <v>-19</v>
-      </c>
-      <c r="K8" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>10</v>
-      </c>
-      <c r="O8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
+      <c r="A1" s="1" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q8"/>
-  <conditionalFormatting sqref="D2:D8">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G8">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J8">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K8">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
+  <autoFilter ref="A1:A1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados_tracker/tracker_dados.xlsx
+++ b/dados_tracker/tracker_dados.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Agentes'!$A$1:$U$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapas'!$A$1:$A$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Mapas'!$A$1:$Q$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1873,17 +1873,602 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Map Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Top Agents</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Win %</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Wins</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Losses</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>K/D</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ADR</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ACS</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>DDΔ</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>HS%</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Aces</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Clutches</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Thrifty</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Flawless</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Plants</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Defuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Haven</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jett (67%); Clove (50%); Phoenix (40%)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H2" t="n">
+        <v>139.1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>204</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K2" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>15</v>
+      </c>
+      <c r="N2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O2" t="n">
+        <v>16</v>
+      </c>
+      <c r="P2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Summit</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Jett (83%); Clove (43%)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>145.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-13</v>
+      </c>
+      <c r="K3" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3</v>
+      </c>
+      <c r="N3" t="n">
+        <v>10</v>
+      </c>
+      <c r="O3" t="n">
+        <v>13</v>
+      </c>
+      <c r="P3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ascent</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sova (60%); Clove (46%)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>150.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P4" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sunset</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Clove (67%)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>11</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H5" t="n">
+        <v>147.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
+        <v>18</v>
+      </c>
+      <c r="P5" t="n">
+        <v>34</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Lotus</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Jett (50%); Clove (30%)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="H6" t="n">
+        <v>140</v>
+      </c>
+      <c r="I6" t="n">
+        <v>213.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="K6" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>10</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Breeze</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Sova (40%); Clove (33%); Jett (20%)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H7" t="n">
+        <v>143.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>213.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9</v>
+      </c>
+      <c r="O7" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>44</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mapa</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Clove (22%); Jett (0%)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="H8" t="n">
+        <v>139.4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-19</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A1"/>
+  <autoFilter ref="A1:Q8"/>
+  <conditionalFormatting sqref="D2:D8">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G8">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H8">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I8">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J8">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K8">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="00F8696B"/>
+        <color rgb="00FFEB84"/>
+        <color rgb="0063BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>